--- a/totales_x_distrito.xlsx
+++ b/totales_x_distrito.xlsx
@@ -4771,7 +4771,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141">
@@ -5360,7 +5360,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F187" t="n">
         <v>0</v>
@@ -6972,7 +6972,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212">
@@ -9483,7 +9483,7 @@
         <v>0</v>
       </c>
       <c r="G292" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="293">
@@ -9545,7 +9545,7 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="295">
@@ -10630,7 +10630,7 @@
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="330">
@@ -11957,7 +11957,7 @@
         </is>
       </c>
       <c r="E372" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F372" t="n">
         <v>0</v>
